--- a/power_data.xlsx
+++ b/power_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="21970" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="power_data" sheetId="1" r:id="rId1"/>
@@ -5761,14 +5761,14 @@
       <c r="B263" t="s">
         <v>5</v>
       </c>
-      <c r="C263">
-        <v>0</v>
+      <c r="C263" s="2">
+        <v>85.7599999999999</v>
       </c>
       <c r="D263" s="2">
         <v>58.29</v>
       </c>
-      <c r="E263">
-        <v>-58.29</v>
+      <c r="E263" s="2">
+        <v>27.4699999999999</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -6254,14 +6254,14 @@
       <c r="B292" t="s">
         <v>5</v>
       </c>
-      <c r="C292">
-        <v>950.04</v>
+      <c r="C292" s="2">
+        <v>79.2899999999999</v>
       </c>
       <c r="D292" s="2">
         <v>52.9199999999999</v>
       </c>
-      <c r="E292">
-        <v>897.12</v>
+      <c r="E292" s="2">
+        <v>26.37</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -12374,14 +12374,14 @@
       <c r="B652" t="s">
         <v>17</v>
       </c>
-      <c r="C652">
-        <v>0</v>
+      <c r="C652" s="2">
+        <v>50.98</v>
       </c>
       <c r="D652" s="2">
         <v>49.27</v>
       </c>
-      <c r="E652">
-        <v>-49.27</v>
+      <c r="E652" s="2">
+        <v>1.70999999999997</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -12868,13 +12868,13 @@
         <v>17</v>
       </c>
       <c r="C681" s="2">
-        <v>99.66</v>
+        <v>48.68</v>
       </c>
       <c r="D681" s="2">
         <v>47.05</v>
       </c>
       <c r="E681" s="2">
-        <v>52.61</v>
+        <v>1.62999999999999</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -27831,10 +27831,10 @@
         <v>138.4</v>
       </c>
       <c r="D1561" s="2">
-        <v>17.9399999999999</v>
-      </c>
-      <c r="E1561" s="2">
-        <v>120.46</v>
+        <v>143.409999999999</v>
+      </c>
+      <c r="E1561">
+        <v>-5.00999999999987</v>
       </c>
     </row>
     <row r="1562" spans="1:5">
@@ -28324,10 +28324,10 @@
         <v>146.569999999999</v>
       </c>
       <c r="D1590" s="2">
-        <v>277.31</v>
+        <v>151.84</v>
       </c>
       <c r="E1590">
-        <v>-130.74</v>
+        <v>-5.27000000000009</v>
       </c>
     </row>
     <row r="1591" spans="1:5">
@@ -30615,14 +30615,14 @@
       <c r="B1725" t="s">
         <v>17</v>
       </c>
-      <c r="C1725" s="2">
-        <v>5.19000000000005</v>
+      <c r="C1725">
+        <v>148</v>
       </c>
       <c r="D1725" s="2">
         <v>91.9900000000001</v>
       </c>
-      <c r="E1725">
-        <v>-86.8</v>
+      <c r="E1725" s="2">
+        <v>56.0099999999998</v>
       </c>
     </row>
     <row r="1726" spans="1:5">
@@ -72028,13 +72028,13 @@
         <v>17</v>
       </c>
       <c r="C4161">
-        <v>745</v>
+        <v>563</v>
       </c>
       <c r="D4161" s="2">
         <v>348.199999999999</v>
       </c>
       <c r="E4161" s="2">
-        <v>396.8</v>
+        <v>214.8</v>
       </c>
     </row>
     <row r="4162" spans="1:5">
@@ -77944,13 +77944,13 @@
         <v>17</v>
       </c>
       <c r="C4509">
-        <v>775</v>
+        <v>931</v>
       </c>
       <c r="D4509" s="2">
         <v>402.199999999999</v>
       </c>
       <c r="E4509" s="2">
-        <v>372.8</v>
+        <v>528.8</v>
       </c>
     </row>
     <row r="4510" spans="1:5">
